--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -520,7 +520,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>용도구역</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -567,7 +567,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>용도구역</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -614,7 +614,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>용도구역</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -739,7 +739,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>용도지구</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>용도지구</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -880,7 +880,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>용도지구</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -927,7 +927,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>용도구역</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -974,7 +974,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>용도구역</t>
+          <t>용도지역지구구역</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3986,7 +3986,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>층수</t>
+          <t>지상층수</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">

--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,16 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>참판정</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>거짓판정</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -537,6 +547,8 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -584,6 +596,8 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -631,6 +645,8 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -670,6 +686,8 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -709,6 +727,8 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -756,6 +776,8 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -803,6 +825,8 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -850,6 +874,8 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -897,6 +923,8 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -944,6 +972,8 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -991,6 +1021,8 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1018,7 +1050,11 @@
           <t>https://www.law.go.kr/법령/국토의계획및이용에관한법률/제58조</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -1026,6 +1062,8 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1053,7 +1091,11 @@
           <t>https://www.law.go.kr/법령/국토의계획및이용에관한법률/제63조</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1061,6 +1103,8 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1089,13 +1133,23 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>도시군계획시설</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1123,7 +1177,11 @@
           <t>https://www.law.go.kr/법령/국토의계획및이용에관한법률/제76조</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1131,6 +1189,8 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1158,7 +1218,11 @@
           <t>https://www.law.go.kr/법령/국토의계획및이용에관한법률/제77조</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1166,6 +1230,8 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1193,7 +1259,11 @@
           <t>https://www.law.go.kr/법령/국토의계획및이용에관한법률/제78조</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1201,6 +1271,8 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1229,13 +1301,23 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>is_empty</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1264,13 +1346,27 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>개발제한구역</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1299,13 +1395,27 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>도시자연공원구역</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1333,7 +1443,11 @@
           <t>https://www.law.go.kr/법령/국토의계획및이용에관한법률/제80조의3</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1341,6 +1455,8 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1369,13 +1485,27 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>시가화조정구역</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1404,13 +1534,35 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>count_gte</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1439,13 +1591,27 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>건물용도</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>교정 및 군사 시설</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1473,7 +1639,11 @@
           <t>https://www.law.go.kr/법령/급경사지재해예방에관한법률/제10조</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1481,6 +1651,8 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1509,13 +1681,34 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H27">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1544,13 +1737,34 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H28">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1579,13 +1793,34 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H29">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1614,13 +1849,34 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H30">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1649,13 +1905,34 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H31">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1684,13 +1961,34 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H32">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1726,6 +2024,8 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1761,6 +2061,8 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1796,6 +2098,8 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1831,6 +2135,8 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1866,6 +2172,8 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1901,6 +2209,8 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1936,6 +2246,8 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1971,6 +2283,8 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2006,6 +2320,8 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2041,6 +2357,8 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2076,6 +2394,8 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2111,6 +2431,8 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2146,6 +2468,8 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2181,6 +2505,8 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2216,6 +2542,8 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2251,6 +2579,8 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2286,6 +2616,8 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2321,6 +2653,8 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2356,6 +2690,8 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2391,6 +2727,8 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2426,6 +2764,8 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2461,6 +2801,8 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2496,6 +2838,8 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2531,6 +2875,8 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2566,6 +2912,8 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2601,6 +2949,8 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2636,6 +2986,8 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2671,6 +3023,8 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2706,6 +3060,8 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2741,6 +3097,8 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2776,6 +3134,8 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2811,6 +3171,8 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2846,6 +3208,8 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2881,6 +3245,8 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2916,6 +3282,8 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2951,6 +3319,8 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2986,6 +3356,8 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -1138,7 +1138,11 @@
           <t>도시군계획시설</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>대상</t>
@@ -1686,9 +1690,10 @@
           <t>읍면</t>
         </is>
       </c>
-      <c r="H27">
-        <f>=</f>
-        <v/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1742,9 +1747,10 @@
           <t>읍면</t>
         </is>
       </c>
-      <c r="H28">
-        <f>=</f>
-        <v/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1798,9 +1804,10 @@
           <t>읍면</t>
         </is>
       </c>
-      <c r="H29">
-        <f>=</f>
-        <v/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1854,9 +1861,10 @@
           <t>읍면</t>
         </is>
       </c>
-      <c r="H30">
-        <f>=</f>
-        <v/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1910,9 +1918,10 @@
           <t>읍면</t>
         </is>
       </c>
-      <c r="H31">
-        <f>=</f>
-        <v/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1966,9 +1975,10 @@
           <t>읍면</t>
         </is>
       </c>
-      <c r="H32">
-        <f>=</f>
-        <v/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>

--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -2026,7 +2026,11 @@
           <t>https://www.law.go.kr/법령/댐주변지역친환경보전및활용에관한특별법/제8조</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2064,15 +2068,35 @@
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>도로구역</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2101,9 +2125,21 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>접도구역</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2138,9 +2174,21 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>공원</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2175,15 +2223,35 @@
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>공원</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2211,7 +2279,11 @@
           <t>https://www.law.go.kr/법령/독도등도서지역의생태계보전에관한특별법/제8조</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2249,15 +2321,35 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>항만구역</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">

--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,16 +490,6 @@
           <t>비고</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>참판정</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>거짓판정</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,8 +537,6 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,8 +584,6 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -645,8 +631,6 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -676,7 +660,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -686,8 +670,6 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -717,7 +699,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -727,8 +709,6 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -776,8 +756,6 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -825,8 +803,6 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,8 +850,6 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -923,8 +897,6 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -972,8 +944,6 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1021,8 +991,6 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1052,7 +1020,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1062,8 +1030,6 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1093,7 +1059,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1103,8 +1069,6 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1152,8 +1116,6 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1183,7 +1145,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1193,8 +1155,6 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1224,7 +1184,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1234,8 +1194,6 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1265,7 +1223,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1275,8 +1233,6 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1320,8 +1276,6 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1369,8 +1323,6 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1418,8 +1370,6 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1449,7 +1399,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>비대상</t>
+          <t>대상아님</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1459,8 +1409,6 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1508,8 +1456,6 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1557,16 +1503,6 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1614,8 +1550,6 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1645,7 +1579,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1655,8 +1589,6 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1704,16 +1636,6 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1761,16 +1683,6 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1818,16 +1730,6 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1875,16 +1777,6 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1932,16 +1824,6 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1989,16 +1871,6 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2028,7 +1900,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>확인필요</t>
+          <t>검토필요</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2038,8 +1910,6 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2087,16 +1957,6 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2144,8 +2004,6 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2193,8 +2051,6 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2242,16 +2098,6 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2281,7 +2127,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>비대상</t>
+          <t>대상아님</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2291,8 +2137,6 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2340,16 +2184,6 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>비대상</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2359,34 +2193,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>매장문화재 보호 및 조사에 관한 법률</t>
+          <t>국가유산영향진단법</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>제6조</t>
+          <t>제9조</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매장문화재 지표조사</t>
+          <t>영향진단의 대상 및 시기</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.law.go.kr/법령/매장문화재보호및조사에관한법률/제6조</t>
+          <t>https://www.law.go.kr/법령/국가유산영향진단법/제9조</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>대지면적</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>30000</v>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2396,34 +2238,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>매장문화재 보호 및 조사에 관한 법률</t>
+          <t>국가유산영향진단법</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>제8조</t>
+          <t>제17조</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>매장문화재 유존지역에서의 개발사업 협의</t>
+          <t>약식영향진단의 대상</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.law.go.kr/법령/매장문화재보호및조사에관한법률/제8조</t>
+          <t>https://www.law.go.kr/법령/국가유산영향진단법/제17조</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>역사문화환경보존지역</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2459,8 +2311,6 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2496,8 +2346,6 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2533,8 +2381,6 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2570,8 +2416,6 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2607,8 +2451,6 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2644,8 +2486,6 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2681,8 +2521,6 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2718,8 +2556,6 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2755,8 +2591,6 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2792,8 +2626,6 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2829,8 +2661,6 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2866,8 +2696,6 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2903,8 +2731,6 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2940,8 +2766,6 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2977,8 +2801,6 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3014,8 +2836,6 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3051,8 +2871,6 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3088,8 +2906,6 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3125,8 +2941,6 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3162,8 +2976,6 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3199,8 +3011,6 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3236,8 +3046,6 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3273,8 +3081,6 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3310,8 +3116,6 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3347,8 +3151,6 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3384,8 +3186,6 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3421,8 +3221,6 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3458,8 +3256,6 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>역사문화환경보존지역</t>
+          <t>역사문화환경 보존지역</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>건물용도</t>
+          <t>건물용도표시</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>교정 및 군사 시설</t>
+          <t>국방·군사시설</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>역사문화환경보존지역</t>
+          <t>역사문화환경 보존지역</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -2304,9 +2304,21 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>건물용도</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>창고시설</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2339,9 +2351,21 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>산림보호구역</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2374,9 +2398,21 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>임야</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2409,9 +2445,21 @@
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>임야</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2444,9 +2492,21 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>임야</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2479,9 +2539,21 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>임야</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2514,9 +2586,21 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>국가지정문화유산구역</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2549,9 +2633,21 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>과밀억제권역</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2584,9 +2680,21 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>성장관리권역</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -2619,9 +2727,21 @@
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>자연보전권역</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -2654,9 +2774,21 @@
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>상수원보호구역</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -2689,9 +2821,21 @@
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>습지보호지역,습지주변관리지역</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -2724,9 +2868,21 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>읍면</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -2759,9 +2915,21 @@
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>역사문화권정비구역</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -2794,9 +2962,21 @@
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>지구단위계획구역</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -2829,9 +3009,21 @@
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>연구개발특구</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -2864,9 +3056,21 @@
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>공원</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -2899,9 +3103,21 @@
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>공원</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -2934,9 +3150,21 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>자연환경보전지역,보전관리지역,보전녹지지역</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -2969,9 +3197,21 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>시·도 생태·경관보전지역</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -3004,9 +3244,21 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>지목</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>종교용지</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
@@ -3039,9 +3291,21 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>무선방위측정장치보호구역</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3074,9 +3338,21 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>철도보호지구</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
@@ -3109,9 +3385,21 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>하천구역</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -3144,9 +3432,21 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>택지개발지구</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
@@ -3178,7 +3478,11 @@
           <t>https://www.law.go.kr/법령/동·서·남해안및내륙권발전특별법/제10조</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3214,9 +3518,21 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>혁신도시개발예정지구</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -3249,9 +3565,21 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>특별대책지역</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>

--- a/regulations_full.xlsx
+++ b/regulations_full.xlsx
@@ -3596,7 +3596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3665,6 +3665,26 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>기준항목3</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>연산자3</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>기준값3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>조건연결</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3693,13 +3713,27 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>건물용도</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>count_gte</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3727,7 +3761,11 @@
           <t>https://www.law.go.kr/법령/건축법/제23조</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -3735,6 +3773,10 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3762,7 +3804,11 @@
           <t>https://www.law.go.kr/법령/건축법/제40조</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -3770,6 +3816,10 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3798,13 +3848,39 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>대지면적</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>200</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>not_contains_any</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>녹지지역,자연녹지지역,보전녹지지역,생산녹지지역</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3835,25 +3911,53 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>제1종일반주거지역,제2종일반주거지역,제3종일반주거지역,준주거지역,중심상업지역,일반상업지역,근린상업지역,유통상업지역,상업지역,준공업지역</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>건물용도</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>문화 및 집회시설,종교시설,판매시설,운수시설,업무시설,숙박시설</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>시행령 제27조의2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>연면적</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="P6" t="n">
         <v>5000</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>시행령 제27조의2. 용도조건(문화집회/종교/판매/운수/업무/숙박) 및 지역요건 별도 반영 필요</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3881,7 +3985,11 @@
           <t>https://www.law.go.kr/법령/건축법/제44조</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -3889,6 +3997,10 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3916,7 +4028,11 @@
           <t>https://www.law.go.kr/법령/건축법/제46조</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -3924,6 +4040,10 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3951,7 +4071,11 @@
           <t>https://www.law.go.kr/법령/건축법/제47조</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -3959,6 +4083,10 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3986,7 +4114,11 @@
           <t>https://www.law.go.kr/법령/건축법/제48조</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -3994,6 +4126,10 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4021,7 +4157,11 @@
           <t>https://www.law.go.kr/법령/건축법/제48조의4</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -4029,6 +4169,10 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4056,7 +4200,11 @@
           <t>https://www.law.go.kr/법령/건축법/제49조</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -4064,6 +4212,10 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4091,7 +4243,11 @@
           <t>https://www.law.go.kr/법령/건축법/제50조</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -4099,6 +4255,10 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4127,13 +4287,41 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>지상층수</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>높이</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>120</v>
+      </c>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4162,13 +4350,29 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>방화지구</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4196,7 +4400,11 @@
           <t>https://www.law.go.kr/법령/건축법/제52조</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -4204,6 +4412,10 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4231,7 +4443,11 @@
           <t>https://www.law.go.kr/법령/건축법/제52조의2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -4239,6 +4455,10 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4267,13 +4487,27 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>지하층수</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4302,13 +4536,29 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>건물용도</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>주택,근린생활시설,문화 및 집회시설,교육연구시설,노유자시설,수련시설,업무시설,숙박시설</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4336,7 +4586,11 @@
           <t>https://www.law.go.kr/법령/건축법/제54조</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -4344,6 +4598,10 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4371,7 +4629,11 @@
           <t>https://www.law.go.kr/법령/건축법/제57조</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -4379,6 +4641,10 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4406,7 +4672,11 @@
           <t>https://www.law.go.kr/법령/건축법/제58조</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -4414,6 +4684,10 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4441,7 +4715,11 @@
           <t>https://www.law.go.kr/법령/건축법/제59조</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -4449,6 +4727,10 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4476,7 +4758,11 @@
           <t>https://www.law.go.kr/법령/건축법/제60조</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -4484,6 +4770,10 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4512,13 +4802,33 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>용도지역지구구역</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>contains_any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>제1종전용주거지역,제2종전용주거지역,제1종일반주거지역,제2종일반주거지역,제3종일반주거지역</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>준주거지역 제외(건축법 제61조는 전용/일반주거지역만 해당)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4546,7 +4856,11 @@
           <t>https://www.law.go.kr/법령/건축법/제62조</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -4554,6 +4868,10 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4613,6 +4931,10 @@
           <t>건축법 제64조제1항. 시행령 제89조 예외 별도 확인</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4640,7 +4962,11 @@
           <t>https://www.law.go.kr/법령/건축법/제68조</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -4648,6 +4974,10 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4675,7 +5005,11 @@
           <t>https://www.law.go.kr/법령/건축법/제84조</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>검토필요</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -4683,6 +5017,10 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4718,6 +5056,10 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4753,6 +5095,10 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4788,6 +5134,10 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4823,6 +5173,10 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4858,6 +5212,10 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4893,6 +5251,10 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4928,6 +5290,10 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4963,6 +5329,10 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4998,6 +5368,10 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5033,6 +5407,10 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5068,6 +5446,10 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5103,6 +5485,10 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5138,6 +5524,10 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5173,6 +5563,10 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5208,6 +5602,10 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5243,6 +5641,10 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5278,6 +5680,10 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5313,6 +5719,10 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5348,6 +5758,10 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5383,6 +5797,10 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5418,6 +5836,10 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5453,6 +5875,10 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5488,6 +5914,10 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5523,6 +5953,10 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5558,6 +5992,10 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5593,6 +6031,10 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5628,6 +6070,10 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5663,6 +6109,10 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5698,6 +6148,10 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5733,6 +6187,10 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5768,6 +6226,10 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5803,6 +6265,10 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5838,6 +6304,10 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5873,6 +6343,10 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5908,6 +6382,10 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5943,6 +6421,10 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5978,6 +6460,10 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6013,6 +6499,10 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6048,6 +6538,10 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6083,6 +6577,10 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6118,6 +6616,10 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6153,6 +6655,10 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6188,6 +6694,10 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6223,6 +6733,10 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
